--- a/data/output/2025/evaluasi_72.xlsx
+++ b/data/output/2025/evaluasi_72.xlsx
@@ -20,6 +20,7 @@
     <sheet name="7209" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="7210" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="7271" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="7212" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1407,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,6 +1524,230 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.721001102714176</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>31.7393452968084</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2840539661056957</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.2461658439048</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2794841084041947</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.099669162393004</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-3.360323438278877</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7208</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1765741580591252</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1625,6 +1850,202 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.41818552637493</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>21.47265986836885</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.266694213677207</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.900199057274024</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3083259863734282</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.549368332004317</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7209</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tojo Una-Una</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.5165596741428695</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1639,7 +2060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,6 +2120,258 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.684987447505799</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.66445499282286</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.225545231837491</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.395406433576015</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.937063706555766</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.729520647172191</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1126731048786194</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1510238179724006</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7210</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sigi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3082738083050841</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1713,7 +2386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1801,6 +2474,528 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.181021382672055</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>26.65821240277278</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.693682264058127</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.331926235331784</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.963524712022086</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.03108076360169635</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.908910464066991</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7271</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Palu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4868496386180672</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9.872927118161593</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20.33897762662399</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.665126072447858</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.743712845961918</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.056690162146023</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.279517073252255</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06456193074701835</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2255312755781335</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7212</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.972657735498932</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1815,7 +3010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2099,6 +3294,230 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.17675217787501</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>25.24703243517134</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.585678487616939</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.916750010055686</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.588112756570725</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1533706261137037</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6903897082650087</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7211</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Laut</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.6269348005177208</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2113,7 +3532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2425,6 +3844,174 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>22.18271862009198</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.333717459103268</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-7.608367465884271</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9.002330176191796</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-2.914796755295479</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7205</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Donggala</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8.391852402580385</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2439,7 +4026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2695,6 +4282,174 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>27.72686097620592</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.95737517895253</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1265343069117031</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.16632369266052</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.074999260723115</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7201</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.440714738396228</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2709,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2797,6 +4552,174 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>26.80978249947928</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-6.033398063705959</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.500180250709482</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2792396690741539</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.053929012501686</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7203</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Morowali</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.3735155433691</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2811,7 +4734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3151,6 +5074,286 @@
       <c r="F12" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>30.72173189919454</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.799615691449879</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-5.907663381910057</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>9.265857204575624</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3.561119926792461</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.936216530737667</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6.766774991674955</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.00553110568615</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.920362641750918</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7204</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Poso</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.1175479685263336</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3165,7 +5368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3225,6 +5428,258 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.876192222712153</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.732626802959347</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>74.03824937553067</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.98898364862285</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.484220856933061</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.58154210631777</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.21388585128153</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.318465615322764</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7202</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Banggai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2394885801189598</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3239,7 +5694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3607,6 +6062,342 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>46.00831550559678</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-7.057911450053091</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.848235471223606</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3.73291858844656</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7443301169472791</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-5.756254232306458</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>21.03449060430719</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.4122583780069911</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-4.783513893178603</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14.00923345480833</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6.825136372457728</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7206</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Toli-Toli</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.567351949474737</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3621,7 +6412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3740,6 +6531,286 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14.43232220350618</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.725849824653363</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.859908385304691</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.692767805206325</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.05467955554961</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.989117881835427</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.985837734345847</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8285745463656</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3006634407181575</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7207</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Buol</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-4.428821285745356</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
